--- a/artfynd/A 55591-2024 artfynd.xlsx
+++ b/artfynd/A 55591-2024 artfynd.xlsx
@@ -20131,10 +20131,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>121152425</v>
+        <v>121152423</v>
       </c>
       <c r="B182" t="n">
-        <v>91967</v>
+        <v>91977</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20175,10 +20175,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>756059</v>
+        <v>755931</v>
       </c>
       <c r="R182" t="n">
-        <v>7458610</v>
+        <v>7458580</v>
       </c>
       <c r="S182" t="n">
         <v>5</v>
@@ -20245,7 +20245,7 @@
         <v>121152424</v>
       </c>
       <c r="B183" t="n">
-        <v>91992</v>
+        <v>92002</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20353,10 +20353,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>121152423</v>
+        <v>121152425</v>
       </c>
       <c r="B184" t="n">
-        <v>91967</v>
+        <v>91977</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -20397,10 +20397,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>755931</v>
+        <v>756059</v>
       </c>
       <c r="R184" t="n">
-        <v>7458580</v>
+        <v>7458610</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>

--- a/artfynd/A 55591-2024 artfynd.xlsx
+++ b/artfynd/A 55591-2024 artfynd.xlsx
@@ -20131,10 +20131,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>121152423</v>
+        <v>121152424</v>
       </c>
       <c r="B182" t="n">
-        <v>91977</v>
+        <v>92002</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20147,21 +20147,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>4365</v>
+        <v>232140</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -20175,10 +20175,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>755931</v>
+        <v>755954</v>
       </c>
       <c r="R182" t="n">
-        <v>7458580</v>
+        <v>7458590</v>
       </c>
       <c r="S182" t="n">
         <v>5</v>
@@ -20242,10 +20242,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>121152424</v>
+        <v>121152423</v>
       </c>
       <c r="B183" t="n">
-        <v>92002</v>
+        <v>91977</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20258,21 +20258,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>232140</v>
+        <v>4365</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -20286,10 +20286,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>755954</v>
+        <v>755931</v>
       </c>
       <c r="R183" t="n">
-        <v>7458590</v>
+        <v>7458580</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>

--- a/artfynd/A 55591-2024 artfynd.xlsx
+++ b/artfynd/A 55591-2024 artfynd.xlsx
@@ -20134,7 +20134,7 @@
         <v>121152424</v>
       </c>
       <c r="B182" t="n">
-        <v>92002</v>
+        <v>92014</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20242,10 +20242,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>121152423</v>
+        <v>121152425</v>
       </c>
       <c r="B183" t="n">
-        <v>91977</v>
+        <v>91989</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20286,10 +20286,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>755931</v>
+        <v>756059</v>
       </c>
       <c r="R183" t="n">
-        <v>7458580</v>
+        <v>7458610</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -20353,10 +20353,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>121152425</v>
+        <v>121152423</v>
       </c>
       <c r="B184" t="n">
-        <v>91977</v>
+        <v>91989</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -20397,10 +20397,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>756059</v>
+        <v>755931</v>
       </c>
       <c r="R184" t="n">
-        <v>7458610</v>
+        <v>7458580</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>

--- a/artfynd/A 55591-2024 artfynd.xlsx
+++ b/artfynd/A 55591-2024 artfynd.xlsx
@@ -20131,10 +20131,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>121152424</v>
+        <v>121152425</v>
       </c>
       <c r="B182" t="n">
-        <v>92014</v>
+        <v>91990</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20147,21 +20147,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>232140</v>
+        <v>4365</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -20175,10 +20175,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>755954</v>
+        <v>756059</v>
       </c>
       <c r="R182" t="n">
-        <v>7458590</v>
+        <v>7458610</v>
       </c>
       <c r="S182" t="n">
         <v>5</v>
@@ -20242,10 +20242,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>121152425</v>
+        <v>121152424</v>
       </c>
       <c r="B183" t="n">
-        <v>91989</v>
+        <v>92015</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20258,21 +20258,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>4365</v>
+        <v>232140</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -20286,10 +20286,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>756059</v>
+        <v>755954</v>
       </c>
       <c r="R183" t="n">
-        <v>7458610</v>
+        <v>7458590</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -20356,7 +20356,7 @@
         <v>121152423</v>
       </c>
       <c r="B184" t="n">
-        <v>91989</v>
+        <v>91990</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>

--- a/artfynd/A 55591-2024 artfynd.xlsx
+++ b/artfynd/A 55591-2024 artfynd.xlsx
@@ -20134,7 +20134,7 @@
         <v>121152425</v>
       </c>
       <c r="B182" t="n">
-        <v>91990</v>
+        <v>91993</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>121152424</v>
       </c>
       <c r="B183" t="n">
-        <v>92015</v>
+        <v>92018</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20356,7 +20356,7 @@
         <v>121152423</v>
       </c>
       <c r="B184" t="n">
-        <v>91990</v>
+        <v>91993</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>

--- a/artfynd/A 55591-2024 artfynd.xlsx
+++ b/artfynd/A 55591-2024 artfynd.xlsx
@@ -20242,10 +20242,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>121152424</v>
+        <v>121152423</v>
       </c>
       <c r="B183" t="n">
-        <v>92018</v>
+        <v>91993</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20258,21 +20258,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>232140</v>
+        <v>4365</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -20286,10 +20286,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>755954</v>
+        <v>755931</v>
       </c>
       <c r="R183" t="n">
-        <v>7458590</v>
+        <v>7458580</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -20353,10 +20353,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>121152423</v>
+        <v>121152424</v>
       </c>
       <c r="B184" t="n">
-        <v>91993</v>
+        <v>92018</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -20369,21 +20369,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>4365</v>
+        <v>232140</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -20397,10 +20397,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>755931</v>
+        <v>755954</v>
       </c>
       <c r="R184" t="n">
-        <v>7458580</v>
+        <v>7458590</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>

--- a/artfynd/A 55591-2024 artfynd.xlsx
+++ b/artfynd/A 55591-2024 artfynd.xlsx
@@ -996,7 +996,7 @@
         <v>119358123</v>
       </c>
       <c r="B5" t="n">
-        <v>91844</v>
+        <v>92008</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>119358124</v>
       </c>
       <c r="B6" t="n">
-        <v>91844</v>
+        <v>92008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>119358031</v>
       </c>
       <c r="B7" t="n">
-        <v>86412</v>
+        <v>86262</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>119358154</v>
       </c>
       <c r="B9" t="n">
-        <v>91852</v>
+        <v>92016</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>119358208</v>
       </c>
       <c r="B10" t="n">
-        <v>89252</v>
+        <v>89403</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>119358083</v>
       </c>
       <c r="B11" t="n">
-        <v>91463</v>
+        <v>91630</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>119358179</v>
       </c>
       <c r="B56" t="n">
-        <v>91832</v>
+        <v>91996</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>119358250</v>
       </c>
       <c r="B57" t="n">
-        <v>91834</v>
+        <v>91998</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
         <v>119358242</v>
       </c>
       <c r="B59" t="n">
-        <v>91834</v>
+        <v>91998</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
         <v>119358119</v>
       </c>
       <c r="B61" t="n">
-        <v>91821</v>
+        <v>91988</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         <v>119358219</v>
       </c>
       <c r="B66" t="n">
-        <v>91840</v>
+        <v>92004</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>119358036</v>
       </c>
       <c r="B67" t="n">
-        <v>86412</v>
+        <v>86262</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>119358155</v>
       </c>
       <c r="B70" t="n">
-        <v>91852</v>
+        <v>92016</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>119358248</v>
       </c>
       <c r="B72" t="n">
-        <v>91834</v>
+        <v>91998</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>119358029</v>
       </c>
       <c r="B73" t="n">
-        <v>86412</v>
+        <v>86262</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>119358246</v>
       </c>
       <c r="B74" t="n">
-        <v>91834</v>
+        <v>91998</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>119358120</v>
       </c>
       <c r="B75" t="n">
-        <v>91821</v>
+        <v>91988</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>119358186</v>
       </c>
       <c r="B76" t="n">
-        <v>91832</v>
+        <v>91996</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         <v>119358182</v>
       </c>
       <c r="B77" t="n">
-        <v>91832</v>
+        <v>91996</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>119358039</v>
       </c>
       <c r="B80" t="n">
-        <v>86412</v>
+        <v>86262</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>119358037</v>
       </c>
       <c r="B81" t="n">
-        <v>86412</v>
+        <v>86262</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>119358028</v>
       </c>
       <c r="B82" t="n">
-        <v>86412</v>
+        <v>86262</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>119358085</v>
       </c>
       <c r="B85" t="n">
-        <v>91463</v>
+        <v>91630</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10054,7 +10054,7 @@
         <v>119358038</v>
       </c>
       <c r="B87" t="n">
-        <v>86412</v>
+        <v>86262</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         <v>119358197</v>
       </c>
       <c r="B89" t="n">
-        <v>89230</v>
+        <v>89381</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
         <v>119358183</v>
       </c>
       <c r="B90" t="n">
-        <v>91832</v>
+        <v>91996</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>119358032</v>
       </c>
       <c r="B92" t="n">
-        <v>86412</v>
+        <v>86262</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>119358035</v>
       </c>
       <c r="B93" t="n">
-        <v>86412</v>
+        <v>86262</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>119358106</v>
       </c>
       <c r="B94" t="n">
-        <v>89263</v>
+        <v>89414</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>119358245</v>
       </c>
       <c r="B99" t="n">
-        <v>91834</v>
+        <v>91998</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
         <v>119358180</v>
       </c>
       <c r="B100" t="n">
-        <v>91832</v>
+        <v>91996</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11538,7 +11538,7 @@
         <v>119358030</v>
       </c>
       <c r="B101" t="n">
-        <v>86412</v>
+        <v>86262</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>119358243</v>
       </c>
       <c r="B102" t="n">
-        <v>91834</v>
+        <v>91998</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
         <v>119358109</v>
       </c>
       <c r="B104" t="n">
-        <v>91828</v>
+        <v>91992</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>119358125</v>
       </c>
       <c r="B105" t="n">
-        <v>91844</v>
+        <v>92008</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>119358153</v>
       </c>
       <c r="B107" t="n">
-        <v>91852</v>
+        <v>92016</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>119358206</v>
       </c>
       <c r="B108" t="n">
-        <v>89252</v>
+        <v>89403</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>119358244</v>
       </c>
       <c r="B109" t="n">
-        <v>91834</v>
+        <v>91998</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>119358018</v>
       </c>
       <c r="B116" t="n">
-        <v>87406</v>
+        <v>88563</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>119358121</v>
       </c>
       <c r="B117" t="n">
-        <v>91821</v>
+        <v>91988</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13447,7 +13447,7 @@
         <v>119358249</v>
       </c>
       <c r="B119" t="n">
-        <v>91834</v>
+        <v>91998</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>119358247</v>
       </c>
       <c r="B120" t="n">
-        <v>91834</v>
+        <v>91998</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
         <v>119358193</v>
       </c>
       <c r="B123" t="n">
-        <v>88153</v>
+        <v>88737</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14189,7 +14189,7 @@
         <v>119358240</v>
       </c>
       <c r="B126" t="n">
-        <v>91834</v>
+        <v>91998</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>119358241</v>
       </c>
       <c r="B127" t="n">
-        <v>91834</v>
+        <v>91998</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14507,7 +14507,7 @@
         <v>119358205</v>
       </c>
       <c r="B129" t="n">
-        <v>89252</v>
+        <v>89403</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
         <v>119358082</v>
       </c>
       <c r="B130" t="n">
-        <v>91463</v>
+        <v>91630</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14719,7 +14719,7 @@
         <v>119358126</v>
       </c>
       <c r="B131" t="n">
-        <v>91844</v>
+        <v>92008</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         <v>119358187</v>
       </c>
       <c r="B132" t="n">
-        <v>91832</v>
+        <v>91996</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15037,7 +15037,7 @@
         <v>119358207</v>
       </c>
       <c r="B134" t="n">
-        <v>89252</v>
+        <v>89403</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         <v>119358239</v>
       </c>
       <c r="B137" t="n">
-        <v>91834</v>
+        <v>91998</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -16097,7 +16097,7 @@
         <v>119358086</v>
       </c>
       <c r="B144" t="n">
-        <v>91463</v>
+        <v>91630</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>119358034</v>
       </c>
       <c r="B148" t="n">
-        <v>86412</v>
+        <v>86262</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16627,7 +16627,7 @@
         <v>119358084</v>
       </c>
       <c r="B149" t="n">
-        <v>91463</v>
+        <v>91630</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16733,7 +16733,7 @@
         <v>119358081</v>
       </c>
       <c r="B150" t="n">
-        <v>91463</v>
+        <v>91630</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16839,7 +16839,7 @@
         <v>119358087</v>
       </c>
       <c r="B151" t="n">
-        <v>91463</v>
+        <v>91630</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16945,7 +16945,7 @@
         <v>119358210</v>
       </c>
       <c r="B152" t="n">
-        <v>89252</v>
+        <v>89403</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
         <v>119358105</v>
       </c>
       <c r="B154" t="n">
-        <v>89263</v>
+        <v>89414</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>

--- a/artfynd/A 55591-2024 artfynd.xlsx
+++ b/artfynd/A 55591-2024 artfynd.xlsx
@@ -996,7 +996,7 @@
         <v>119358123</v>
       </c>
       <c r="B5" t="n">
-        <v>92008</v>
+        <v>92022</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>119358124</v>
       </c>
       <c r="B6" t="n">
-        <v>92008</v>
+        <v>92022</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>119358031</v>
       </c>
       <c r="B7" t="n">
-        <v>86262</v>
+        <v>86276</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>119358154</v>
       </c>
       <c r="B9" t="n">
-        <v>92016</v>
+        <v>92030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>119358208</v>
       </c>
       <c r="B10" t="n">
-        <v>89403</v>
+        <v>89417</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>119358083</v>
       </c>
       <c r="B11" t="n">
-        <v>91630</v>
+        <v>91644</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>119358179</v>
       </c>
       <c r="B56" t="n">
-        <v>91996</v>
+        <v>92010</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>119358250</v>
       </c>
       <c r="B57" t="n">
-        <v>91998</v>
+        <v>92012</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
         <v>119358242</v>
       </c>
       <c r="B59" t="n">
-        <v>91998</v>
+        <v>92012</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
         <v>119358119</v>
       </c>
       <c r="B61" t="n">
-        <v>91988</v>
+        <v>92002</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         <v>119358219</v>
       </c>
       <c r="B66" t="n">
-        <v>92004</v>
+        <v>92018</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>119358036</v>
       </c>
       <c r="B67" t="n">
-        <v>86262</v>
+        <v>86276</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>119358155</v>
       </c>
       <c r="B70" t="n">
-        <v>92016</v>
+        <v>92030</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>119358248</v>
       </c>
       <c r="B72" t="n">
-        <v>91998</v>
+        <v>92012</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>119358029</v>
       </c>
       <c r="B73" t="n">
-        <v>86262</v>
+        <v>86276</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>119358246</v>
       </c>
       <c r="B74" t="n">
-        <v>91998</v>
+        <v>92012</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>119358120</v>
       </c>
       <c r="B75" t="n">
-        <v>91988</v>
+        <v>92002</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>119358186</v>
       </c>
       <c r="B76" t="n">
-        <v>91996</v>
+        <v>92010</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         <v>119358182</v>
       </c>
       <c r="B77" t="n">
-        <v>91996</v>
+        <v>92010</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>119358039</v>
       </c>
       <c r="B80" t="n">
-        <v>86262</v>
+        <v>86276</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>119358037</v>
       </c>
       <c r="B81" t="n">
-        <v>86262</v>
+        <v>86276</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>119358028</v>
       </c>
       <c r="B82" t="n">
-        <v>86262</v>
+        <v>86276</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>119358085</v>
       </c>
       <c r="B85" t="n">
-        <v>91630</v>
+        <v>91644</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10054,7 +10054,7 @@
         <v>119358038</v>
       </c>
       <c r="B87" t="n">
-        <v>86262</v>
+        <v>86276</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         <v>119358197</v>
       </c>
       <c r="B89" t="n">
-        <v>89381</v>
+        <v>89395</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
         <v>119358183</v>
       </c>
       <c r="B90" t="n">
-        <v>91996</v>
+        <v>92010</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>119358032</v>
       </c>
       <c r="B92" t="n">
-        <v>86262</v>
+        <v>86276</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>119358035</v>
       </c>
       <c r="B93" t="n">
-        <v>86262</v>
+        <v>86276</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>119358106</v>
       </c>
       <c r="B94" t="n">
-        <v>89414</v>
+        <v>89428</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>119358245</v>
       </c>
       <c r="B99" t="n">
-        <v>91998</v>
+        <v>92012</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
         <v>119358180</v>
       </c>
       <c r="B100" t="n">
-        <v>91996</v>
+        <v>92010</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11538,7 +11538,7 @@
         <v>119358030</v>
       </c>
       <c r="B101" t="n">
-        <v>86262</v>
+        <v>86276</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>119358243</v>
       </c>
       <c r="B102" t="n">
-        <v>91998</v>
+        <v>92012</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
         <v>119358109</v>
       </c>
       <c r="B104" t="n">
-        <v>91992</v>
+        <v>92006</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>119358125</v>
       </c>
       <c r="B105" t="n">
-        <v>92008</v>
+        <v>92022</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>119358153</v>
       </c>
       <c r="B107" t="n">
-        <v>92016</v>
+        <v>92030</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>119358206</v>
       </c>
       <c r="B108" t="n">
-        <v>89403</v>
+        <v>89417</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>119358244</v>
       </c>
       <c r="B109" t="n">
-        <v>91998</v>
+        <v>92012</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>119358018</v>
       </c>
       <c r="B116" t="n">
-        <v>88563</v>
+        <v>88577</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>119358121</v>
       </c>
       <c r="B117" t="n">
-        <v>91988</v>
+        <v>92002</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13447,7 +13447,7 @@
         <v>119358249</v>
       </c>
       <c r="B119" t="n">
-        <v>91998</v>
+        <v>92012</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>119358247</v>
       </c>
       <c r="B120" t="n">
-        <v>91998</v>
+        <v>92012</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
         <v>119358193</v>
       </c>
       <c r="B123" t="n">
-        <v>88737</v>
+        <v>88751</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14189,7 +14189,7 @@
         <v>119358240</v>
       </c>
       <c r="B126" t="n">
-        <v>91998</v>
+        <v>92012</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>119358241</v>
       </c>
       <c r="B127" t="n">
-        <v>91998</v>
+        <v>92012</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14507,7 +14507,7 @@
         <v>119358205</v>
       </c>
       <c r="B129" t="n">
-        <v>89403</v>
+        <v>89417</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
         <v>119358082</v>
       </c>
       <c r="B130" t="n">
-        <v>91630</v>
+        <v>91644</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14719,7 +14719,7 @@
         <v>119358126</v>
       </c>
       <c r="B131" t="n">
-        <v>92008</v>
+        <v>92022</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         <v>119358187</v>
       </c>
       <c r="B132" t="n">
-        <v>91996</v>
+        <v>92010</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15037,7 +15037,7 @@
         <v>119358207</v>
       </c>
       <c r="B134" t="n">
-        <v>89403</v>
+        <v>89417</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         <v>119358239</v>
       </c>
       <c r="B137" t="n">
-        <v>91998</v>
+        <v>92012</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -16097,7 +16097,7 @@
         <v>119358086</v>
       </c>
       <c r="B144" t="n">
-        <v>91630</v>
+        <v>91644</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>119358034</v>
       </c>
       <c r="B148" t="n">
-        <v>86262</v>
+        <v>86276</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16627,7 +16627,7 @@
         <v>119358084</v>
       </c>
       <c r="B149" t="n">
-        <v>91630</v>
+        <v>91644</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16733,7 +16733,7 @@
         <v>119358081</v>
       </c>
       <c r="B150" t="n">
-        <v>91630</v>
+        <v>91644</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16839,7 +16839,7 @@
         <v>119358087</v>
       </c>
       <c r="B151" t="n">
-        <v>91630</v>
+        <v>91644</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16945,7 +16945,7 @@
         <v>119358210</v>
       </c>
       <c r="B152" t="n">
-        <v>89403</v>
+        <v>89417</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
         <v>119358105</v>
       </c>
       <c r="B154" t="n">
-        <v>89414</v>
+        <v>89428</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>

--- a/artfynd/A 55591-2024 artfynd.xlsx
+++ b/artfynd/A 55591-2024 artfynd.xlsx
@@ -996,7 +996,7 @@
         <v>119358123</v>
       </c>
       <c r="B5" t="n">
-        <v>92022</v>
+        <v>92024</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>119358124</v>
       </c>
       <c r="B6" t="n">
-        <v>92022</v>
+        <v>92024</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>119358031</v>
       </c>
       <c r="B7" t="n">
-        <v>86276</v>
+        <v>86278</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>119358154</v>
       </c>
       <c r="B9" t="n">
-        <v>92030</v>
+        <v>92032</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>119358208</v>
       </c>
       <c r="B10" t="n">
-        <v>89417</v>
+        <v>89419</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>119358083</v>
       </c>
       <c r="B11" t="n">
-        <v>91644</v>
+        <v>91646</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>119358179</v>
       </c>
       <c r="B56" t="n">
-        <v>92010</v>
+        <v>92012</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>119358250</v>
       </c>
       <c r="B57" t="n">
-        <v>92012</v>
+        <v>92014</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
         <v>119358242</v>
       </c>
       <c r="B59" t="n">
-        <v>92012</v>
+        <v>92014</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
         <v>119358119</v>
       </c>
       <c r="B61" t="n">
-        <v>92002</v>
+        <v>92004</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         <v>119358219</v>
       </c>
       <c r="B66" t="n">
-        <v>92018</v>
+        <v>92020</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>119358036</v>
       </c>
       <c r="B67" t="n">
-        <v>86276</v>
+        <v>86278</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>119358155</v>
       </c>
       <c r="B70" t="n">
-        <v>92030</v>
+        <v>92032</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>119358248</v>
       </c>
       <c r="B72" t="n">
-        <v>92012</v>
+        <v>92014</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>119358029</v>
       </c>
       <c r="B73" t="n">
-        <v>86276</v>
+        <v>86278</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>119358246</v>
       </c>
       <c r="B74" t="n">
-        <v>92012</v>
+        <v>92014</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>119358120</v>
       </c>
       <c r="B75" t="n">
-        <v>92002</v>
+        <v>92004</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>119358186</v>
       </c>
       <c r="B76" t="n">
-        <v>92010</v>
+        <v>92012</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         <v>119358182</v>
       </c>
       <c r="B77" t="n">
-        <v>92010</v>
+        <v>92012</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>119358039</v>
       </c>
       <c r="B80" t="n">
-        <v>86276</v>
+        <v>86278</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>119358037</v>
       </c>
       <c r="B81" t="n">
-        <v>86276</v>
+        <v>86278</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>119358028</v>
       </c>
       <c r="B82" t="n">
-        <v>86276</v>
+        <v>86278</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>119358085</v>
       </c>
       <c r="B85" t="n">
-        <v>91644</v>
+        <v>91646</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10054,7 +10054,7 @@
         <v>119358038</v>
       </c>
       <c r="B87" t="n">
-        <v>86276</v>
+        <v>86278</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         <v>119358197</v>
       </c>
       <c r="B89" t="n">
-        <v>89395</v>
+        <v>89397</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
         <v>119358183</v>
       </c>
       <c r="B90" t="n">
-        <v>92010</v>
+        <v>92012</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>119358032</v>
       </c>
       <c r="B92" t="n">
-        <v>86276</v>
+        <v>86278</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>119358035</v>
       </c>
       <c r="B93" t="n">
-        <v>86276</v>
+        <v>86278</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>119358106</v>
       </c>
       <c r="B94" t="n">
-        <v>89428</v>
+        <v>89430</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>119358245</v>
       </c>
       <c r="B99" t="n">
-        <v>92012</v>
+        <v>92014</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
         <v>119358180</v>
       </c>
       <c r="B100" t="n">
-        <v>92010</v>
+        <v>92012</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11538,7 +11538,7 @@
         <v>119358030</v>
       </c>
       <c r="B101" t="n">
-        <v>86276</v>
+        <v>86278</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>119358243</v>
       </c>
       <c r="B102" t="n">
-        <v>92012</v>
+        <v>92014</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
         <v>119358109</v>
       </c>
       <c r="B104" t="n">
-        <v>92006</v>
+        <v>92008</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>119358125</v>
       </c>
       <c r="B105" t="n">
-        <v>92022</v>
+        <v>92024</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>119358153</v>
       </c>
       <c r="B107" t="n">
-        <v>92030</v>
+        <v>92032</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>119358206</v>
       </c>
       <c r="B108" t="n">
-        <v>89417</v>
+        <v>89419</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>119358244</v>
       </c>
       <c r="B109" t="n">
-        <v>92012</v>
+        <v>92014</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>119358018</v>
       </c>
       <c r="B116" t="n">
-        <v>88577</v>
+        <v>88579</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>119358121</v>
       </c>
       <c r="B117" t="n">
-        <v>92002</v>
+        <v>92004</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13447,7 +13447,7 @@
         <v>119358249</v>
       </c>
       <c r="B119" t="n">
-        <v>92012</v>
+        <v>92014</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>119358247</v>
       </c>
       <c r="B120" t="n">
-        <v>92012</v>
+        <v>92014</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
         <v>119358193</v>
       </c>
       <c r="B123" t="n">
-        <v>88751</v>
+        <v>88753</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14189,7 +14189,7 @@
         <v>119358240</v>
       </c>
       <c r="B126" t="n">
-        <v>92012</v>
+        <v>92014</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>119358241</v>
       </c>
       <c r="B127" t="n">
-        <v>92012</v>
+        <v>92014</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14507,7 +14507,7 @@
         <v>119358205</v>
       </c>
       <c r="B129" t="n">
-        <v>89417</v>
+        <v>89419</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
         <v>119358082</v>
       </c>
       <c r="B130" t="n">
-        <v>91644</v>
+        <v>91646</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14719,7 +14719,7 @@
         <v>119358126</v>
       </c>
       <c r="B131" t="n">
-        <v>92022</v>
+        <v>92024</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         <v>119358187</v>
       </c>
       <c r="B132" t="n">
-        <v>92010</v>
+        <v>92012</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15037,7 +15037,7 @@
         <v>119358207</v>
       </c>
       <c r="B134" t="n">
-        <v>89417</v>
+        <v>89419</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         <v>119358239</v>
       </c>
       <c r="B137" t="n">
-        <v>92012</v>
+        <v>92014</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -16097,7 +16097,7 @@
         <v>119358086</v>
       </c>
       <c r="B144" t="n">
-        <v>91644</v>
+        <v>91646</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>119358034</v>
       </c>
       <c r="B148" t="n">
-        <v>86276</v>
+        <v>86278</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16627,7 +16627,7 @@
         <v>119358084</v>
       </c>
       <c r="B149" t="n">
-        <v>91644</v>
+        <v>91646</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16733,7 +16733,7 @@
         <v>119358081</v>
       </c>
       <c r="B150" t="n">
-        <v>91644</v>
+        <v>91646</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16839,7 +16839,7 @@
         <v>119358087</v>
       </c>
       <c r="B151" t="n">
-        <v>91644</v>
+        <v>91646</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16945,7 +16945,7 @@
         <v>119358210</v>
       </c>
       <c r="B152" t="n">
-        <v>89417</v>
+        <v>89419</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
         <v>119358105</v>
       </c>
       <c r="B154" t="n">
-        <v>89428</v>
+        <v>89430</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
